--- a/Assets/Samples/MainDemo/Excels/Networks/Cmds/NetworkCmds.xlsx
+++ b/Assets/Samples/MainDemo/Excels/Networks/Cmds/NetworkCmds.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26860" windowHeight="12660"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="NetworkCmds" sheetId="1" r:id="rId1"/>

--- a/Assets/Samples/MainDemo/Excels/Networks/Cmds/NetworkCmds.xlsx
+++ b/Assets/Samples/MainDemo/Excels/Networks/Cmds/NetworkCmds.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16660"/>
+    <workbookView windowWidth="26860" windowHeight="14500"/>
   </bookViews>
   <sheets>
     <sheet name="NetworkCmds" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
   <si>
     <t>##comment</t>
   </si>
@@ -84,6 +84,21 @@
   </si>
   <si>
     <t>TGAServer</t>
+  </si>
+  <si>
+    <t>AppConfig</t>
+  </si>
+  <si>
+    <t>拉取GM后台应用配置URL</t>
+  </si>
+  <si>
+    <t>HTTP_POST</t>
+  </si>
+  <si>
+    <t>GameServer</t>
+  </si>
+  <si>
+    <t>/v1/common/app-config</t>
   </si>
 </sst>
 </file>
@@ -769,7 +784,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -787,6 +802,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1133,7 +1151,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
   <dimension ref="A1:U41"/>
   <sheetFormatPr defaultColWidth="13" defaultRowHeight="16.8"/>
@@ -1276,7 +1294,25 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1"/>
+    <row r="6" ht="22" customHeight="1" spans="1:21">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>AppCustomConfig</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
     <row r="7" ht="22" customHeight="1"/>
     <row r="8" ht="22" customHeight="1"/>
     <row r="9" ht="22" customHeight="1"/>
